--- a/09_Project_Management_Evidence/Risk_Issue_Change_Register.xlsx
+++ b/09_Project_Management_Evidence/Risk_Issue_Change_Register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gedion\Desktop\TrackWIL\09_Project_Management_Evidence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEF5C30-A4F3-4FB6-A1E2-4992D3AE0286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D04AD0-DCB9-431E-8FEF-BD618EE583C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15480" yWindow="660" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>PROJECT RISK, ISSUE &amp; CHANGE REGISTER</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>Documented in Chapter 3.</t>
+  </si>
+  <si>
+    <t>Fixed on 23 Oct 2026: signed session cookie (commit 5268c2e); DEF-01 closed after retest TC-121.</t>
+  </si>
+  <si>
+    <t>Fixed on 23 Oct 2026 (commit 5268c2e); DEF-02 closed after retest TC-137.</t>
   </si>
 </sst>
 </file>
@@ -1189,13 +1195,13 @@
         <v>60</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K13" s="6">
         <v>46320</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -1221,19 +1227,19 @@
         <v>16</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>63</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K14" s="6">
         <v>46321</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
